--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_324_Guinea.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_324_Guinea.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rd777dc53ed404987"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R4893bbbd2e704a8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rfc73b788d75a472a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R307492d9b1dc4329"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R3a840a0bd0ef46de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rfea0c0ae5f134f50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rc2b3b9a5d64d46f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Re2c565540dc945b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R244ceba785c545c7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rfa7bfda941e14fb2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rde122ad1d884422e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R8a9fc58843bc45f2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ324CommercialTable" displayName="EEZ324CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ324CommercialTable" displayName="EEZ324CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ324FunctionalTable" displayName="EEZ324FunctionalTable" ref="A1:O25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O25"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ324FunctionalTable" displayName="EEZ324FunctionalTable" ref="A1:E25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E25"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ324ValidationTable" displayName="EEZ324ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ324ValidationTable" displayName="EEZ324ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -14161,7 +14115,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4aa1196f3ee84f2e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfee25a2fba9c4067"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14171,20 +14125,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -14192,660 +14136,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>3.8772279892999997</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>3.8772279892999997</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$202,A2,'Species'!$U$2:$U$202))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>499.48372190277945</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>499.48372190277945</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1598.3224702893997</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.454060491013279</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2844.857327813129</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1598.3224702893997</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2903.6249875545823</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$202,A3,'Species'!$U$2:$U$202))</x:f>
-        <x:v>4640929.062902267</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.454060491013279</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2844.857327813129</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>4546999.391811181</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>93929.67109108623</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0206575068517156</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.02065750685171562</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1317.0582032093</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.2951117773764325</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>197.2930457540094</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1317.0582032093</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>223.14200295198054</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$202,A4,'Species'!$U$2:$U$202))</x:f>
-        <x:v>293891.0054684598</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.2951117773764325</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>197.2930457540094</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>259846.42434646585</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>34044.58112199395</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.1310180858082568</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.13101808580825672</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>6782.0643445201995</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.519255683282892</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>330.5640975930907</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>6782.0643445201995</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>344.2530323805406</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$202,A5,'Species'!$U$2:$U$202))</x:f>
-        <x:v>2334746.2164010224</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.519255683282892</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>330.5640975930907</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>2241906.979864596</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>92839.23653642647</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0414108334423553</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.04141083344235525</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>170872.37110491662</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.586155559578135</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>38.561645656838316</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>170872.37110491662</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>43.9003742239353</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$202,A6,'Species'!$U$2:$U$202))</x:f>
-        <x:v>7501361.036036989</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.586155559578135</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>38.561645656838316</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>6589119.827091573</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>912241.2089454159</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.1384465957341798</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.13844659573417983</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>1104.1404747900997</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.0028569100822633</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>10.065999629644903</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>1104.1404747900997</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>10.278172557382103</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$202,A7,'Species'!$U$2:$U$202))</x:f>
-        <x:v>11348.546327482449</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.0028569100822633</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>10.065999629644903</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>11114.277610313091</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>234.26871716935784</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.021078177582318</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.02107817758231778</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>644676.3791013965</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.381113850662125</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>240.4993188353264</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>644676.3791013965</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>278.3617122930025</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$202,A8,'Species'!$U$2:$U$202))</x:f>
-        <x:v>179453220.76151752</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.381113850662125</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>240.4993188353264</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>155044230.04311052</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>24408990.718407005</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.1574324353226173</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.15743243532261736</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>173264.5599335561</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.700190842982063</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>501.4075198356464</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>173264.5599335561</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>659.7826430646494</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$202,A9,'Species'!$U$2:$U$202))</x:f>
-        <x:v>114316949.30239499</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.700190842982063</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>501.4075198356464</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>86876153.27169907</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>27440796.030695915</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.3158610849731889</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.3158610849731888</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>72.2098524102</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.8697208325560823</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>740.8338751628421</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>72.2098524102</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>774.556181030206</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$202,A10,'Species'!$U$2:$U$202))</x:f>
-        <x:v>55930.58751559933</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.8697208325560823</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>740.8338751628421</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>53495.50478598536</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>2435.0827296139687</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.045519389701168</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.04551938970116806</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>5803.2172942824</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.129850034380654</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1348.4971545223789</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>5803.2172942824</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1637.8156041908833</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$202,A11,'Species'!$U$2:$U$202))</x:f>
-        <x:v>9504599.839086112</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.129850034380654</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1348.4971545223789</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>7825622.008414875</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>1678977.8306712369</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.2145488024933782</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.21454880249337824</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>7142.4535885633995</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.400522869576171</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2514.9124426481785</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>7142.4535885633995</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2545.8286280448206</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$202,A12,'Species'!$U$2:$U$202))</x:f>
-        <x:v>18183462.820246164</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.400522869576171</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2514.9124426481785</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>17962645.400915228</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>220817.41933093593</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0122931458258195</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.012293145825819448</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2d3a7e0382e24b22"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R364ec67732d046b1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14855,20 +14370,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -14876,1362 +14381,478 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>123072.13324001759</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.806792527962339</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>640.9033298065058</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>123072.13324001759</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>643.3388165723827</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$202,A2,'Species'!$U$2:$U$202))</x:f>
-        <x:v>79177080.55167152</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.806792527962339</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>640.9033298065058</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>78877339.99991721</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>299740.5517543107</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0038000844317851</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.003800084431785166</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1.771836873</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.14</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1380.3842646028838</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1.771836873</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1380.3842646028838</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$202,A3,'Species'!$U$2:$U$202))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>2445.8157389323783</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.14</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1380.3842646028838</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>2445.8157389323783</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>9.2512021785</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.34</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2187.761623949552</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>9.2512021785</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$202,A4,'Species'!$U$2:$U$202))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>20239.425101520792</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.34</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>20239.425101520792</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>142.5823412262</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.099651057986669</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>1257.9143109059237</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>142.5823412262</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>1528.0103435892893</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$202,A5,'Species'!$U$2:$U$202))</x:f>
-        <x:v>217867.29220681114</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.099651057986669</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>1257.9143109059237</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>179356.36751090863</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>38510.924695902504</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.2147173542280858</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.21471735422808577</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>9057.724677557799</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.8089343116177425</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>644.0718402915527</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>9057.724677557799</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>651.3494603726834</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$202,A6,'Species'!$U$2:$U$202))</x:f>
-        <x:v>5899744.08093161</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.8089343116177425</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>644.0718402915527</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>5833825.401928863</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>65918.67900274787</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0112993918160378</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.011299391816037707</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>7076.3356529171</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.400225574541788</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2513.191455708147</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>7076.3356529171</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2544.1101479562017</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$202,A7,'Species'!$U$2:$U$202))</x:f>
-        <x:v>18002977.344930667</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.400225574541788</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2513.191455708147</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>17784186.300634187</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>218791.04429648072</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.012302561421586</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.012302561421586018</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>974.205070271</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.597130495525036</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>395.4854365139653</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>974.205070271</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>400.6838711111917</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$202,A8,'Species'!$U$2:$U$202))</x:f>
-        <x:v>390348.2588123348</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.597130495525036</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>395.4854365139653</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>385283.91747024463</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>5064.341342090163</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0131444400154108</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.013144440015410923</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>121.69914856910002</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.873331542353887</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>747.0188183030915</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>121.69914856910002</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>938.5409340586762</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$202,A9,'Species'!$U$2:$U$202))</x:f>
-        <x:v>114219.63257218873</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.873331542353887</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>747.0188183030915</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>90911.55415258146</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>23308.078419607264</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.2563819157737435</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.25638191577374353</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>4798.465572354</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>4.239976802620174</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>1737.7080084374395</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>4798.465572354</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1895.165298326243</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$202,A10,'Species'!$U$2:$U$202))</x:f>
-        <x:v>9093885.437938474</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>4.239976802620174</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>1737.7080084374395</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>8338332.053290888</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>755553.3846475864</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0906120528444765</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.09061205284447653</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>14.9826340518</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>2.7637799011840105</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>58.047016286069834</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>14.9826340518</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>67.40018948399003</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$202,A11,'Species'!$U$2:$U$202))</x:f>
-        <x:v>1009.8323740606014</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>2.7637799011840105</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>58.047016286069834</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>869.6972028130591</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>140.1351712475423</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.1611309899517572</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.16113098995175712</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>1773.4753689433996</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.445311702977079</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2788.121548611254</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>1773.4753689433996</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2876.209780640604</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$202,A12,'Species'!$U$2:$U$202))</x:f>
-        <x:v>5100887.20188021</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.445311702977079</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2788.121548611254</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>4944664.892082387</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>156222.30979782343</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0315941147089611</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.03159411470896105</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>1544.7318639900002</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>4.080692855727688</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>1204.1840091267318</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>1544.7318639900002</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1204.612053881852</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$202,A13,'Species'!$U$2:$U$202))</x:f>
-        <x:v>1860802.6233777357</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>4.080692855727688</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>1204.1840091267318</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>1860141.4090052878</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>661.2143724479247</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.0003554645734174</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.0003554645734173025</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>9390.067368665099</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.297150713785666</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>198.2214797069097</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>9390.067368665099</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>277.23903250094696</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$202,A14,'Species'!$U$2:$U$202))</x:f>
-        <x:v>2603293.192407425</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.297150713785666</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>198.2214797069097</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>1861313.0483643638</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>741980.1440430612</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.398632645215204</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.3986326452152039</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>561169.89043013</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.3223657383509666</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>210.07082370697785</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>561169.89043013</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>235.45557574914727</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$202,A15,'Species'!$U$2:$U$202))</x:f>
-        <x:v>132130579.64431214</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.3223657383509666</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>210.07082370697785</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>117885421.1222119</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>14245158.52210024</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.120839017976042</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.12083901797604195</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>180993.83499750853</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>2.9383878922036377</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>86.77365528257569</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>180993.83499750853</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>292.0479614909913</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$202,A16,'Species'!$U$2:$U$202))</x:f>
-        <x:v>52858880.55345921</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>2.9383878922036377</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>86.77365528257569</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>15705496.646345189</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>37153383.90711402</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>3.365629355360752</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>2.365629355360752</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>16906.0378436046</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.1279299125562883</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>134.2548280120629</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>16906.0378436046</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>513.4295707558236</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$202,A17,'Species'!$U$2:$U$202))</x:f>
-        <x:v>8680059.75322362</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.1279299125562883</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>134.2548280120629</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>2269717.2030585622</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>6410342.550165058</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>3.82429130004689</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>2.82429130004689</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>1104.2132986835998</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>2.002885080566106</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>10.06665258124485</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>1104.2132986835998</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>10.279269794570677</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$202,A18,'Species'!$U$2:$U$202))</x:f>
-        <x:v>11350.506407921575</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>2.002885080566106</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>10.06665258124485</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>11115.731653438152</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>234.77475448342375</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0211209447837657</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.021120944783765694</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>1302.0755691575</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.3012256706477725</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>200.09013196347735</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>1302.0755691575</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>224.9340821930221</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$202,A19,'Species'!$U$2:$U$202))</x:f>
-        <x:v>292881.17309439916</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.3012256706477725</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>200.09013196347735</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>260532.47245914405</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>32348.70063525511</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.1241637955143113</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.12416379551431134</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>39149.843883892805</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.559371051274953</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>362.5526228008204</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>39149.843883892805</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>362.7673429712722</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$202,A20,'Species'!$U$2:$U$202))</x:f>
-        <x:v>14202284.843499906</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.559371051274953</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>362.5526228008204</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>14193878.582347995</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>8406.26115191169</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0005922455305745</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.0005922455305744275</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>47217.657297308906</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>2.810342451163715</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>64.61635429850374</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>47217.657297308906</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>69.45164661177337</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$202,A21,'Species'!$U$2:$U$202))</x:f>
-        <x:v>3279344.0484485202</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>2.810342451163715</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>64.61635429850374</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>3051032.873068243</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>228311.17538027745</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.0748307818626281</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.07483078186262819</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>3.0633018457000003</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.73</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>537.0317963702527</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>3.0633018457000003</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>537.0317963702527</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$202,A22,'Species'!$U$2:$U$202))</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>1645.0904930205818</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.73</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>537.0317963702527</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
-        <x:v>1645.0904930205818</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>6782.0643445201995</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.519255683282892</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>330.5640975930907</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>6782.0643445201995</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>344.2530323805406</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$202,A23,'Species'!$U$2:$U$202))</x:f>
-        <x:v>2334746.2164010224</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.519255683282892</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>330.5640975930907</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>2241906.979864596</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>92839.23653642647</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.0414108334423553</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.04141083344235525</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>26.932628757200003</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.8</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>630.957344480193</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>26.932628757200003</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>630.957344480193</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$202,A24,'Species'!$U$2:$U$202))</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>16993.339920513794</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.8</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>630.957344480193</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
-        <x:v>16993.339920513794</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>3.6140229002</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.97</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>933.2543007969915</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>3.6140229002</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>933.2543007969915</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$202,A25,'Species'!$U$2:$U$202))</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>3372.8024147904666</x:v>
       </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.97</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>933.2543007969915</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
-        <x:v>3372.8024147904666</x:v>
-      </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G25">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O25">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10ea63b97cac4e25"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c259c6615da498c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16406,7 +15027,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -16505,7 +15126,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>336296938.66161853</x:v>
+        <x:v>281411632.6133717</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -16519,7 +15140,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>336296938.66161853</x:v>
+        <x:v>275820022.72623754</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -16533,7 +15154,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-54885306.04824686</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -16547,7 +15168,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-60476915.935380995</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -16558,9 +15179,9 @@
         <x:v>EEZ_324</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -16572,47 +15193,19 @@
         <x:v>EEZ_324</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_324</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_324</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7553f737b4ba47dc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2540b93e4284af4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16659,7 +15252,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
